--- a/דוח נכסים לתאריך:30-07-2026.xlsx
+++ b/דוח נכסים לתאריך:30-07-2026.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="ממצאים" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="עסקים חשודים" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,22 +29,11 @@
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+      <sz val="11"/>
     </font>
     <font>
       <name val="Arial"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <color rgb="000563C1"/>
-      <u val="single"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <i val="1"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="4">
@@ -57,11 +46,13 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F4E79"/>
+        <bgColor rgb="001F4E79"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
+        <fgColor rgb="00FFF3CD"/>
+        <bgColor rgb="00FFF3CD"/>
       </patternFill>
     </fill>
   </fills>
@@ -74,24 +65,16 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="001F4E79"/>
-      </left>
-      <right style="thin">
-        <color rgb="001F4E79"/>
-      </right>
-      <top style="thin">
-        <color rgb="001F4E79"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="001F4E79"/>
-      </bottom>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -99,11 +82,9 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -469,19 +450,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="35" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
     <col width="50" customWidth="1" min="5" max="5"/>
-    <col width="50" customWidth="1" min="6" max="6"/>
-    <col width="50" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25" customHeight="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>שם העסק</t>
@@ -521,17 +502,17 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>מיכלי ששון רפלקסולוגיה</t>
+          <t>רקמת חן</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>הרב זווין 11, ירושלים</t>
+          <t>הרב זווין 49</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>רפלקסולוגיה</t>
+          <t>חנות יודאיקה</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -541,44 +522,390 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>https://www.b144.co.il/b144_sip/401D0D1A4370655D411000114D/</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr"/>
-      <c r="G2" s="2" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>הערות:</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>בניין מגורים — ייתכן עסקים נוספים שאינם ברשומות ציבוריות</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>סריקה בוצעה: אינדקסים 9984–9993 (הרב זווין 10–25, ירושלים)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>תאריך סריקה: 30-07-2026</t>
-        </is>
-      </c>
+          <t>https://www.d.co.il/80045552/52170/</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr"/>
+      <c r="G2" s="3" t="inlineStr"/>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>מיי שופ - my shop</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>הרב כלפון משה הכהן 10</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>חנות אונליין - ריהוט ומוצרי חשמל</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>גבוה</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/80191649/2538/</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr"/>
+      <c r="G3" s="3" t="inlineStr"/>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>איטום סנטר</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>הרב כלפון משה הכהן 18</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>קבלן איטום</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>גבוה</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/80338446/2410/</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr"/>
+      <c r="G4" s="3" t="inlineStr"/>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>מיגונטו</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>הרב כלפון משה הכהן 28</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>מערכות אזעקה ואבטחה</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>גבוה</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/80154968/2280/</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr"/>
+      <c r="G5" s="3" t="inlineStr"/>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>דוידי שיווק</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>הרב כלפון משה הכהן 28</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>שיווק ציוד לגנים ומשחקים</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>גבוה</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/80266774/10895/</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr"/>
+      <c r="G6" s="3" t="inlineStr"/>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>אורן מזגנים וחשמל</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>הרב כלפון משה הכהן 8</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>מיזוג אוויר וחשמל</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>גבוה</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/74938930/26210/</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr"/>
+      <c r="G7" s="3" t="inlineStr"/>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>ליאור הליצן מיץ ופיץ</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>הרב מן ההר 13</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>בידור ואמנות</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>גבוה</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/14563180/3310/</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr"/>
+      <c r="G8" s="3" t="inlineStr"/>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>אשר - מחיצות ותקרות</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>הרב מן ההר 17</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>קבלן מחיצות וגבס</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>גבוה</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/11720300/25410/</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr"/>
+      <c r="G9" s="3" t="inlineStr"/>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>חיים קבלו</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>הרב עוזיאל 127</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>תריסים ואלומיניום</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>גבוה</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/60027110/52080/</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr"/>
+      <c r="G10" s="3" t="inlineStr"/>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>ד"ר אליהו לביא</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>הרב עוזיאל 35</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>נטורופתיה</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>גבוה</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/80022854/40030002/</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr"/>
+      <c r="G11" s="3" t="inlineStr"/>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>א.א.א. אביאור</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>הרב פטאל 26</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>חשמלאי</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>גבוה</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/1826590/17910/</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr"/>
+      <c r="G12" s="3" t="inlineStr"/>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>בן עטר הסעות</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>הרב פטאל 46</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>שירותי הסעות</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>גבוה</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/80135750/870/</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr"/>
+      <c r="G13" s="3" t="inlineStr"/>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>וינברג א. א.</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>הרב צבי יהודה 9</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>הפצת ספרים</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>גבוה</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/15267970/36690/</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr"/>
+      <c r="G14" s="3" t="inlineStr"/>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>כהן מאיר ציון</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>הרב ריינס 5</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>מורה דרך</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>גבוה</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/3208040/24600/</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr"/>
+      <c r="G15" s="3" t="inlineStr"/>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
-  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/דוח נכסים לתאריך:30-07-2026.xlsx
+++ b/דוח נכסים לתאריך:30-07-2026.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="ממצאים" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="נכסים חשודים" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,25 +29,20 @@
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+      <sz val="12"/>
     </font>
     <font>
       <name val="Arial"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
       <color rgb="000563C1"/>
+      <sz val="10"/>
       <u val="single"/>
     </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <i val="1"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -61,7 +56,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
+        <fgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D6E4F0"/>
       </patternFill>
     </fill>
   </fills>
@@ -102,8 +102,12 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -469,12 +473,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
     <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="50" customWidth="1" min="5" max="5"/>
     <col width="50" customWidth="1" min="6" max="6"/>
@@ -518,7 +522,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="20" customHeight="1">
+    <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>מיכלי ששון רפלקסולוגיה</t>
@@ -547,38 +551,645 @@
       <c r="F2" s="2" t="inlineStr"/>
       <c r="G2" s="2" t="inlineStr"/>
     </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>הערות:</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>בניין מגורים — ייתכן עסקים נוספים שאינם ברשומות ציבוריות</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>סריקה בוצעה: אינדקסים 9984–9993 (הרב זווין 10–25, ירושלים)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>תאריך סריקה: 30-07-2026</t>
-        </is>
-      </c>
+    <row r="3" ht="18" customHeight="1">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>ששי גיזום</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>השלשלת 63, ירושלים</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>גיזום עצים</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>גבוה</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/35288580/38635/</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr"/>
+      <c r="G3" s="4" t="inlineStr"/>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>סייטהוד תקשורת באינטרנט בע"מ</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>הרקפת 1, ירושלים</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>שירותי אינטרנט ותקשורת</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>גבוה</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>https://www.b144.co.il/b144_sip/401C04134174635F41140D13/</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr"/>
+      <c r="G4" s="2" t="inlineStr"/>
+    </row>
+    <row r="5" ht="18" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>א.א הסעות</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>הרקפת 1, ירושלים</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>הסעות ותחבורה</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>גבוה</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/80040501/870/</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr"/>
+      <c r="G5" s="4" t="inlineStr"/>
+    </row>
+    <row r="6" ht="18" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>אליה הובלות</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>הרקפת 7, ירושלים</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>הובלות ומעברים</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>גבוה</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/80238639/35840/</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr"/>
+      <c r="G6" s="2" t="inlineStr"/>
+    </row>
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>גן העיר</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>הרקפת 16, ירושלים</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>גינון ושירותי גינון</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>גבוה</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/37720010/11000/</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr"/>
+      <c r="G7" s="4" t="inlineStr"/>
+    </row>
+    <row r="8" ht="18" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>סלק מזיק</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>הרב יוסף חיים שרים 1, ירושלים</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>שירות הדברה</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>גבוה</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>https://easy.co.il/page/3064619</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr"/>
+      <c r="G8" s="2" t="inlineStr"/>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>יוסי מור קליניקה</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>הרב יוסף שרים 5, ירושלים</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>פסיכולוגיה קלינית</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>גבוה</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/80199158/40260/</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr"/>
+      <c r="G9" s="4" t="inlineStr"/>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>אדרמן משה</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>הרב יוסף חיים שרים 20, ירושלים</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>הנדסה אזרחית</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>גבוה</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>https://easy.co.il/page/25996298</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr"/>
+      <c r="G10" s="2" t="inlineStr"/>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>קרית הילד</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>הרב שרירא גאון 4, ירושלים</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>גן ילדים</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>גבוה</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>https://easy.co.il/page/26499697</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr"/>
+      <c r="G11" s="4" t="inlineStr"/>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>משולם האיתן — רפואה משלימה</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>הרב שרירא גאון 7, ירושלים</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>רפואה משלימה</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>גבוה</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/80053470/40030007/</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr"/>
+      <c r="G12" s="2" t="inlineStr"/>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>כולל חזון אלחנן</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>הרב שרירא גאון 7, ירושלים</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>מוסד יהדות ודת</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>גבוה</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>https://www.b144.co.il/b144_sip/4B1503154474/</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr"/>
+      <c r="G13" s="4" t="inlineStr"/>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>קירמה צחי</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>הרב שרירא גאון 10, ירושלים</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>קרמיקה</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>גבוה</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>https://www.b144.co.il/b144_sip/401C04134174625F4D130115/</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr"/>
+      <c r="G14" s="2" t="inlineStr"/>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>אנימל פוד</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>הרב שמואל ברוך 17, ירושלים</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>ציוד ומזון לבעלי חיים</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>גבוה</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>https://easy.co.il/en/page/10086474</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr"/>
+      <c r="G15" s="4" t="inlineStr"/>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>בית כנסת אביר יעקב</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>הרב שמואל נתן 4, ירושלים</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>בית כנסת</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>גבוה</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>https://easy.co.il/page/26409403</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr"/>
+      <c r="G16" s="2" t="inlineStr"/>
+    </row>
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>ד"ר דקל יעל</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>הרב שמואל נתן 12, ירושלים</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>רופאת עיניים</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>גבוה</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>https://easy.co.il/en/page/24560011</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr"/>
+      <c r="G17" s="4" t="inlineStr"/>
+    </row>
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>שנגחאי</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>הרוזמרין 1, ירושלים</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>מסעדה אסייתית</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>גבוה</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>https://easy.co.il/page/25943074</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr"/>
+      <c r="G18" s="2" t="inlineStr"/>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>מסעדת הים התיכון</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>הרוזמרין 2, ירושלים</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>מסעדה ים-תיכונית</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>גבוה</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>https://easy.co.il/en/page/20169687</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr"/>
+      <c r="G19" s="4" t="inlineStr"/>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>הסעות מימוני</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>הרוזמרין 4, ירושלים</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>הסעות</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>גבוה</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/80202068/870/</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr"/>
+      <c r="G20" s="2" t="inlineStr"/>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>קרית הילד הרן</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>הרן 4, ירושלים</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>גן ילדים</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>גבוה</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>https://easy.co.il/en/page/27149411</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr"/>
+      <c r="G21" s="4" t="inlineStr"/>
+    </row>
+    <row r="22" ht="18" customHeight="1">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>פנינה — קוסמטיקאית פרא רפואית</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>הרן 14, ירושלים</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>קוסמטיקה פרא-רפואית</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>גבוה</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/80237965/43860/</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr"/>
+      <c r="G22" s="2" t="inlineStr"/>
+    </row>
+    <row r="23" ht="18" customHeight="1">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>אקשן מדיה מקרנים ופלזמות</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>ניסן הרפז 12, ירושלים</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>השכרת מקרנים ומסכי פלזמה</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>גבוה</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/68616860/41310/</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr"/>
+      <c r="G23" s="4" t="inlineStr"/>
+    </row>
+    <row r="24" ht="18" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>מירב בכור — רפואה משלימה</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>הררי רפול 7, ירושלים</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>רפואה משלימה</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>גבוה</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>https://www.d.co.il/80240342/40030057/</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr"/>
+      <c r="G24" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
-  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>